--- a/storage/xls/Payrolls4.xlsx
+++ b/storage/xls/Payrolls4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kashf_system\storage\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6612638E-D01C-4EF2-B5CF-F0D23B5CD9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1713F82-A89E-463A-82BA-27950A46701A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3225" yWindow="405" windowWidth="14640" windowHeight="15075" xr2:uid="{AB335FC4-EF25-4D47-916C-5FDF28E485F5}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="28920" windowHeight="15600" xr2:uid="{AB335FC4-EF25-4D47-916C-5FDF28E485F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -265,9 +265,6 @@
     <t>عنوان</t>
   </si>
   <si>
-    <t>محافظة</t>
-  </si>
-  <si>
     <t>امر</t>
   </si>
   <si>
@@ -290,6 +287,9 @@
   </si>
   <si>
     <t>منتسب خارجي</t>
+  </si>
+  <si>
+    <t>جهة</t>
   </si>
 </sst>
 </file>
@@ -669,7 +669,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>75</v>
@@ -678,25 +678,25 @@
         <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
@@ -728,7 +728,7 @@
         <v>1000</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
@@ -754,7 +754,7 @@
         <v>46119</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
@@ -774,7 +774,7 @@
         <v>46115</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G4" s="2">
         <v>46120</v>
@@ -806,7 +806,7 @@
         <v>46121</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
